--- a/converted_files/837/home-infusion-ndc.xlsx
+++ b/converted_files/837/home-infusion-ndc.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b5043</t>
+          <t>69e82c69836d7d05c9a0586e</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2417,7 +2417,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b5043</t>
+          <t>69e82c69836d7d05c9a0586e</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2838,7 +2838,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b5043</t>
+          <t>69e82c69836d7d05c9a0586e</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3259,7 +3259,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b5043</t>
+          <t>69e82c69836d7d05c9a0586e</t>
         </is>
       </c>
       <c r="B5"/>
@@ -3680,7 +3680,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b5043</t>
+          <t>69e82c69836d7d05c9a0586e</t>
         </is>
       </c>
       <c r="B6"/>
@@ -4101,7 +4101,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b5043</t>
+          <t>69e82c69836d7d05c9a0586e</t>
         </is>
       </c>
       <c r="B7"/>

--- a/converted_files/837/home-infusion-ndc.xlsx
+++ b/converted_files/837/home-infusion-ndc.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b5043</t>
+          <t>69efef06ad4799caa7f5e4cc</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2417,7 +2417,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b5043</t>
+          <t>69efef06ad4799caa7f5e4cc</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2838,7 +2838,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b5043</t>
+          <t>69efef06ad4799caa7f5e4cc</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3259,7 +3259,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b5043</t>
+          <t>69efef06ad4799caa7f5e4cc</t>
         </is>
       </c>
       <c r="B5"/>
@@ -3680,7 +3680,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b5043</t>
+          <t>69efef06ad4799caa7f5e4cc</t>
         </is>
       </c>
       <c r="B6"/>
@@ -4101,7 +4101,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b5043</t>
+          <t>69efef06ad4799caa7f5e4cc</t>
         </is>
       </c>
       <c r="B7"/>

--- a/converted_files/837/home-infusion-ndc.xlsx
+++ b/converted_files/837/home-infusion-ndc.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a0586e</t>
+          <t>6a04cb3c618f76c4f7b1971f</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2417,7 +2417,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a0586e</t>
+          <t>6a04cb3c618f76c4f7b1971f</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2838,7 +2838,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a0586e</t>
+          <t>6a04cb3c618f76c4f7b1971f</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3259,7 +3259,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a0586e</t>
+          <t>6a04cb3c618f76c4f7b1971f</t>
         </is>
       </c>
       <c r="B5"/>
@@ -3680,7 +3680,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a0586e</t>
+          <t>6a04cb3c618f76c4f7b1971f</t>
         </is>
       </c>
       <c r="B6"/>
@@ -4101,7 +4101,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a0586e</t>
+          <t>6a04cb3c618f76c4f7b1971f</t>
         </is>
       </c>
       <c r="B7"/>

--- a/converted_files/837/home-infusion-ndc.xlsx
+++ b/converted_files/837/home-infusion-ndc.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b1971f</t>
+          <t>6a04cc5c1ef26d534baf422d</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2417,7 +2417,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b1971f</t>
+          <t>6a04cc5c1ef26d534baf422d</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2838,7 +2838,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b1971f</t>
+          <t>6a04cc5c1ef26d534baf422d</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3259,7 +3259,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b1971f</t>
+          <t>6a04cc5c1ef26d534baf422d</t>
         </is>
       </c>
       <c r="B5"/>
@@ -3680,7 +3680,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b1971f</t>
+          <t>6a04cc5c1ef26d534baf422d</t>
         </is>
       </c>
       <c r="B6"/>
@@ -4101,7 +4101,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b1971f</t>
+          <t>6a04cc5c1ef26d534baf422d</t>
         </is>
       </c>
       <c r="B7"/>

--- a/converted_files/837/home-infusion-ndc.xlsx
+++ b/converted_files/837/home-infusion-ndc.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf422d</t>
+          <t>6a0614dff8d6a2fc74349077</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2417,7 +2417,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf422d</t>
+          <t>6a0614dff8d6a2fc74349077</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2838,7 +2838,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf422d</t>
+          <t>6a0614dff8d6a2fc74349077</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3259,7 +3259,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf422d</t>
+          <t>6a0614dff8d6a2fc74349077</t>
         </is>
       </c>
       <c r="B5"/>
@@ -3680,7 +3680,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf422d</t>
+          <t>6a0614dff8d6a2fc74349077</t>
         </is>
       </c>
       <c r="B6"/>
@@ -4101,7 +4101,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf422d</t>
+          <t>6a0614dff8d6a2fc74349077</t>
         </is>
       </c>
       <c r="B7"/>

--- a/converted_files/837/home-infusion-ndc.xlsx
+++ b/converted_files/837/home-infusion-ndc.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a0614dff8d6a2fc74349077</t>
+          <t>6a32cb6597613a0e49909752</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2417,7 +2417,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a0614dff8d6a2fc74349077</t>
+          <t>6a32cb6597613a0e49909752</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2838,7 +2838,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a0614dff8d6a2fc74349077</t>
+          <t>6a32cb6597613a0e49909752</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3259,7 +3259,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a0614dff8d6a2fc74349077</t>
+          <t>6a32cb6597613a0e49909752</t>
         </is>
       </c>
       <c r="B5"/>
@@ -3680,7 +3680,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a0614dff8d6a2fc74349077</t>
+          <t>6a32cb6597613a0e49909752</t>
         </is>
       </c>
       <c r="B6"/>
@@ -4101,7 +4101,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a0614dff8d6a2fc74349077</t>
+          <t>6a32cb6597613a0e49909752</t>
         </is>
       </c>
       <c r="B7"/>
